--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1972,7 +1972,7 @@
         <v>46251.626983587965</v>
       </c>
       <c r="D12" s="5">
-        <v>46252.606471701394</v>
+        <v>46279.74956909722</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2022,8 +2022,8 @@
       <c r="T12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>48</v>
+      <c r="U12" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
